--- a/artfynd/S 1214-2022 artfynd.xlsx
+++ b/artfynd/S 1214-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580567</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580535</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199884</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199830</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1586,6 +1626,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199916</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63181476</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828509</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1958,6 +2013,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63184248</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2090,6 +2150,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828505</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2216,6 +2281,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63200827</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2337,6 +2407,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828567</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2458,6 +2533,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828568</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2569,6 +2649,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580610</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2694,6 +2779,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2820,6 +2910,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202963</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2946,6 +3041,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539638</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3072,6 +3172,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189576</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3198,6 +3303,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225982</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3324,6 +3434,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63228867</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3445,6 +3560,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828564</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3547,6 +3667,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116438691</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3668,6 +3793,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828579</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3789,6 +3919,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828580</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3910,6 +4045,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828581</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4031,6 +4171,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828582</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4152,6 +4297,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828583</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4273,6 +4423,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828584</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4394,6 +4549,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123500</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4515,6 +4675,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123516</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4621,6 +4786,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580583</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4746,6 +4916,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828502</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4852,6 +5027,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580557</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4958,6 +5138,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580702</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5069,6 +5254,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580656</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5190,6 +5380,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828554</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5305,6 +5500,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580685</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5415,6 +5615,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580546</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5526,8 +5731,56 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>